--- a/CSA_parameters.xlsx
+++ b/CSA_parameters.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9536977A-B226-4056-8062-33C9014827EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="9300" tabRatio="621" activeTab="7"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="621" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="8" r:id="rId1"/>
@@ -16,7 +17,7 @@
     <sheet name="AlignedTable" sheetId="16" r:id="rId7"/>
     <sheet name="MetaVariables" sheetId="13" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +30,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="431">
   <si>
     <t>Analysis step</t>
   </si>
@@ -689,9 +691,6 @@
     <t>Mass accuracy to integrate adjacent peaks and match fragments (Da)</t>
   </si>
   <si>
-    <t>IonFiltering</t>
-  </si>
-  <si>
     <t>DDA0014</t>
   </si>
   <si>
@@ -1061,45 +1060,6 @@
   </si>
   <si>
     <t>SMILES</t>
-  </si>
-  <si>
-    <r>
-      <t>Mass accuracy (Da) for "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>IonFiltering</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>" or "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDAspectraIntegration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>"</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1538,9 +1498,6 @@
     <t>inchikey</t>
   </si>
   <si>
-    <t>Minimum spectral entropy similarity score to find similar CSA spectra</t>
-  </si>
-  <si>
     <t>"precursor_intensity" also covers "Precursor_int", "Precursorint" and "PrecursorIntensity" values</t>
   </si>
   <si>
@@ -1562,12 +1519,6 @@
     <t>DIA0023</t>
   </si>
   <si>
-    <t>Minimum spectral entropy similarity score to find similar DIA spectra</t>
-  </si>
-  <si>
-    <t>Minimum spectral entropy similarity score to find similar DDA spectra</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -1604,30 +1555,6 @@
     <t>Filename</t>
   </si>
   <si>
-    <r>
-      <t>Retention time window (min) to group compounds with similar aggregation parameter (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>AT0008</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>) on the first column of the aligned MS/MS table annotation.</t>
-    </r>
-  </si>
-  <si>
     <t>NISTno</t>
   </si>
   <si>
@@ -1791,51 +1718,6 @@
         <family val="2"/>
       </rPr>
       <t>` tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>TRUE or FALSE (When TRUE, it sorts candidate molecular formulas using the `</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sqrt(frequency)/rank</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">` equation, and when FALSE it sorts candidate molecular formulas relative to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>frequency</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> of detections across samples)</t>
     </r>
   </si>
   <si>
@@ -2265,9 +2147,6 @@
     <t>Retention time window (min) to find CSA spectra variants or match reference spreadsheet compounds</t>
   </si>
   <si>
-    <t>Mass window (Da) to match reference spreadsheet compounds</t>
-  </si>
-  <si>
     <t>Retention time window (min) to find DDA spectra variants or match reference spreadsheet compounds</t>
   </si>
   <si>
@@ -2277,9 +2156,6 @@
     <t>Number of parallel threads (only on "Sample Mode" levels)</t>
   </si>
   <si>
-    <t>Mass window (Da) to match reference spreadsheet compounds and to detect similar DDA spectra</t>
-  </si>
-  <si>
     <t>Do not fill when any of PARAM0001-PARAM0003 are selected "YES"</t>
   </si>
   <si>
@@ -2307,9 +2183,6 @@
     </r>
   </si>
   <si>
-    <t>Retention time window (min) to find reoccurring peaks in the IDSL.IPA peaklists</t>
-  </si>
-  <si>
     <t>Retention time window (min) to group reoccurring peaks</t>
   </si>
   <si>
@@ -2424,54 +2297,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> files for untargeted DIA spectra</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Minimum frequency (%) of detection for CSA spectra across all </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>files for untargeted CSA spectra</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Minimum frequency (%) of detection for DDA spectra across all </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.msp </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>files for untargeted DDA spectra</t>
     </r>
   </si>
   <si>
@@ -2579,15 +2404,6 @@
     <t>DIA0025</t>
   </si>
   <si>
-    <t>Address of the reference standard metadata file to generate a list of targeted CSA blocks</t>
-  </si>
-  <si>
-    <t>Address of the reference standard metadata file to generate a list of targeted DDA blocks</t>
-  </si>
-  <si>
-    <t>Address of the reference standard metadata file to generate a list of targeted DIA blocks</t>
-  </si>
-  <si>
     <t>Create a library of unique spectra variants</t>
   </si>
   <si>
@@ -2603,9 +2419,6 @@
     <t>Export aligned CSA spectra plots</t>
   </si>
   <si>
-    <t>"YES" OR "NO", When "YES", fill out CSA0023-CSA0029</t>
-  </si>
-  <si>
     <r>
       <t>Select "peakList" or "alignedTable". "alignedTable" should be selected when the address of the '</t>
     </r>
@@ -2941,9 +2754,6 @@
     </r>
   </si>
   <si>
-    <t>"YES" OR "NO", When "YES", fill out CSA0008, and CSA0030-CSA0039.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">"All" or a list of semicolons separated from selected samples including their extensions with no extra space (case sensitive). You may skip this parameter, if a spreadsheet was provided for </t>
     </r>
@@ -3031,7 +2841,1079 @@
   </si>
   <si>
     <r>
-      <t>≥ 0, Fill when the reference spreadsheet is provided (</t>
+      <t xml:space="preserve">"All" or a list of semicolons separated from selected samples including their extensions with no extra space (case sensitive). You may skip this parameter, if a spreadsheet was provided for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"All" or a list of semicolons separated from selected samples including their extensions with no extra space (case sensitive). You may skip this parameter, if a spreadsheet was provided for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>FSDB file name</t>
+  </si>
+  <si>
+    <t>FSdb0004</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or provide an address to save the FSDB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select "All" to include the entire </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> libraries or a list of semicolon separated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> libraries in the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> format.</t>
+    </r>
+  </si>
+  <si>
+    <t>FSdb0009</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address to save the FSDB library in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.Rdata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> format</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Follow the naming rules in R! IDSL.FSA can generate the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.Rdata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> format</t>
+    </r>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out DIA0012-DIA0021.</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out DIA0022-DIA0028.</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out DDA0012-DDA0018.</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out CSA0012-CSA0022</t>
+  </si>
+  <si>
+    <t>Name of the msp library to generate the FSDB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or provide a spreadsheet in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.xlsx/.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> format with four column headers of 'Filename', 'Name', 'PrecursorMZ', 'Precursor_RT' (case sensitive). For </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files, headers should be  'Name', 'PrecursorMZ', 'Precursor_RT' (case sensitive). You may provide more information in separate columns to enrich the output reference </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files. </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.CSA/wiki/Unique-spectra-aggregation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address of the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> library (INPUT) msp files</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Output location (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files and spectra figures)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Output location (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files and aligned EICs figures)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Output location (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files and EICs)</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.CSA/wiki/DIA-analysis-by-IDSL.CSA</t>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.IPA/wiki/Parallelization-Mode</t>
+  </si>
+  <si>
+    <t>Intensity height threshold for chromatographic peaks of MS level 2 EIC</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files for Data-Independent Acquisition (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) methods such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SWATH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS^E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, and All-Ion Fragmentation (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AIF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) analyses</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>"YES" OR "NO", When "YES", fill out the `</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">` tab. IDSL.CSA automatically detect </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SWATH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AIF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> data.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.CSA/wiki/CSA-analysis-by-IDSL.CSA#csa-msp-generation</t>
+  </si>
+  <si>
+    <t>https://github.com/idslme/IDSL.CSA/wiki/CSA-analysis-by-IDSL.CSA#csa-aggregation-on-the-aligned-table</t>
+  </si>
+  <si>
+    <t>Create unique spectra by measuring pairwise similarity across entire samples</t>
+  </si>
+  <si>
+    <t>InChIKey14</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Default </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FSDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> index number) or any variable from the `</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MetaVariables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">` tab. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>InChIKey14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> performs the aggregation only based on the first 14 letters of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>InChIKeys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRUE or FALSE (When TRUE, it sorts candidate molecular formulas using the `</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sqrt(frequency)/rank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">` equation, and when FALSE it sorts candidate structures relative to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>frequency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of detections across samples)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to ignore precursor m/z. We suggest using a mass error for precursors for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MS^E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>SWATH-MS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AIF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> analyses and skipping this parameter for only one MS level analyses such as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>EI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>in-source fragmentation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Minimum spectral entropy similarity score to find similar spectra</t>
+  </si>
+  <si>
+    <t>Minimum cosine similarity score to find similar spectra</t>
+  </si>
+  <si>
+    <t>CSA0040</t>
+  </si>
+  <si>
+    <t>basePeakMZ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address of the reference standard metadata file to generate a list of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> CSA blocks</t>
+    </r>
+  </si>
+  <si>
+    <t>≥ 0 (Default = 10%)</t>
+  </si>
+  <si>
+    <t>Address to save the IDSL.DDA results</t>
+  </si>
+  <si>
+    <t>DDA0026</t>
+  </si>
+  <si>
+    <t>NA or provide a meta-variable from the reference spreadsheet (DDA0005)</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out DDA0019-DDA0026.</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out CSA0023-CSA0030</t>
+  </si>
+  <si>
+    <t>"YES" OR "NO", When "YES", fill out CSA0008, and CSA0031-CSA0040.</t>
+  </si>
+  <si>
+    <t>"All" or a vector of comma separated IDSL.IPA peak ID indices ONLY when one HRMS file was selected in DDA0005</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Aggregation meta-variable (only when </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is provided)</t>
+    </r>
+  </si>
+  <si>
+    <t>"All" or a vector of comma separated IDSL.IPA peak ID indices ONLY when one HRMS file was selected in DIA0005.</t>
+  </si>
+  <si>
+    <t>Aggregation meta-variable (only when DIA0005 is provided)</t>
+  </si>
+  <si>
+    <r>
+      <t>NA or provide a meta-variable from the reference spreadsheet (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Minimum frequency (%) of detection for DDA spectra across all </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.msp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> files for untargeted DDA spectra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Minimum frequency (%) of detection for CSA spectra across all </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">.msp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>files for untargeted CSA spectra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>≥ 0.001 For targeted analysis using a reference spreadsheet (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), spectra clustering can be performed via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA0019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with or without retention time tolerance. Select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> only when performing targeted analysis.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>≥ 0.001 For targeted analysis using a reference spreadsheet (</t>
     </r>
     <r>
       <rPr>
@@ -3050,12 +3932,227 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0.001 When the reference spreadsheet is provided (</t>
+      <t xml:space="preserve">), spectra clustering can be performed via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CSA0023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with or without retention time tolerance. Select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> only when performing targeted analysis.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>≥ 0.001 For targeted analysis using a reference spreadsheet (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DIA0005</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), spectra clustering can be performed via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDA0022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> with or without retention time tolerance. Select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> only when performing targeted analysis.</t>
+    </r>
+  </si>
+  <si>
+    <t>MostIntenseDDAspectra</t>
+  </si>
+  <si>
+    <r>
+      <t>Mass accuracy (Da) for "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IonFiltering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>", "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>DDAspectraIntegration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>to create unique spectra in the next step</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address of the reference standard metadata file to generate a list of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DDA blocks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address of the reference standard metadata file to generate a list of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> DIA blocks</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> unique spectra generation aggregates spectra based on a meta-variable when a reference set of targeted ions is provided in </t>
     </r>
     <r>
       <rPr>
@@ -3074,36 +4171,111 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">), spectra aggregation is performed only using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">CSA0023 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>regardless of retention time proximity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"All" or a list of semicolons separated from selected samples including their extensions with no extra space (case sensitive). You may skip this parameter, if a spreadsheet was provided for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
+      <t xml:space="preserve">. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>CSA0006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> is set to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, the targeted step is skipped and the analysis proceeds through the untargeted workflow. For more detailed information, please refer to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FSA_uniqueMSPblockTagger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> function in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IDSL.FSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> package.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> unique spectra generation aggregates spectra based on a meta-variable when a reference set of targeted ions is provided in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -3112,29 +4284,11 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"All" or a vector of comma separated IDSL.IPA peak ID indices </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ONLY when one HRMS file was selected in DDA0006</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Aggregation meta-variable (only when </t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
     </r>
     <r>
       <rPr>
@@ -3153,108 +4307,92 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> is provided)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Provide a meta-variable from the reference spreadsheet (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0, Fill when the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0.001 When the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), spectra aggregation is performed only using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA0019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> regardless of retention time proximity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"All" or a list of semicolons separated from selected samples including their extensions with no extra space (case sensitive). You may skip this parameter, if a spreadsheet was provided for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
+      <t xml:space="preserve"> is set to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, the targeted step is skipped and the analysis proceeds through the untargeted workflow. For more detailed information, please refer to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FSA_uniqueMSPblockTagger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> function in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IDSL.FSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> package.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Targeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> unique spectra generation aggregates spectra based on a meta-variable when a reference set of targeted ions is provided in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -3263,37 +4401,11 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">"All" or a vector of comma separated IDSL.IPA peak ID indices </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ONLY when one HRMS file was selected in DIA0006</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Provide a meta-variable from the reference spreadsheet (</t>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. If </t>
     </r>
     <r>
       <rPr>
@@ -3312,112 +4424,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0, Fill when the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0.001 When the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), spectra aggregation is performed only using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA0022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> regardless of retention time proximity.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Aggregation meta-variable (only when </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> is provided)</t>
-    </r>
-  </si>
-  <si>
-    <t>FSDB file name</t>
-  </si>
-  <si>
-    <t>FSdb0004</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Select </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve"> is set to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <i/>
         <sz val="12"/>
         <color theme="1"/>
@@ -3433,12 +4444,104 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> or provide an address to save the FSDB</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Select "All" to include the entire </t>
+      <t xml:space="preserve">, the targeted step is skipped and the analysis proceeds through the untargeted workflow. For more detailed information, please refer to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FSA_uniqueMSPblockTagger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> function in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IDSL.FSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> package.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Untargeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> unique spectra generation is used to aggregate spectra </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>first by precursor ion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>then by base peak ions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> within each cluster of similar spectra. For more detailed information, please refer to the </t>
     </r>
     <r>
       <rPr>
@@ -3448,25 +4551,35 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> libraries or a list of semicolon separated</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> libraries in the </t>
+      <t>FSA_uniqueMSPblockTaggerUntargeted</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> function in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>IDSL.FSA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> package. The unique msp file will be automatically annotated using the parameters in the `</t>
     </r>
     <r>
       <rPr>
@@ -3476,738 +4589,54 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> format.</t>
-    </r>
-  </si>
-  <si>
-    <t>FSdb0009</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Address to save the FSDB library in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.Rdata</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> format</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Follow the naming rules in R! IDSL.FSA can generate the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.Rdata</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> format</t>
-    </r>
-  </si>
-  <si>
-    <t>"YES" OR "NO", When "YES", fill out DIA0012-DIA0021.</t>
-  </si>
-  <si>
-    <t>"YES" OR "NO", When "YES", fill out DIA0022-DIA0028.</t>
-  </si>
-  <si>
-    <t>"YES" OR "NO", When "YES", fill out DDA0012-DDA0018.</t>
-  </si>
-  <si>
-    <t>"YES" OR "NO", When "YES", fill out DDA0019-DDA0025.</t>
-  </si>
-  <si>
-    <t>"YES" OR "NO", When "YES", fill out CSA0012-CSA0022</t>
-  </si>
-  <si>
-    <t>Name of the msp library to generate the FSDB</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Select </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> or provide a spreadsheet in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.xlsx/.csv</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> format with four column headers of 'Filename', 'Name', 'PrecursorMZ', 'Precursor_RT' (case sensitive). For </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files, headers should be  'Name', 'PrecursorMZ', 'Precursor_RT' (case sensitive). You may provide more information in separate columns to enrich the output reference </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files. </t>
-    </r>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.CSA/wiki/Unique-spectra-aggregation</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Address of the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> library (INPUT) msp files</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Output location (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files and spectra figures)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Output location (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files and aligned EICs figures)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Output location (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files and EICs)</t>
-    </r>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.CSA/wiki/DIA-analysis-by-IDSL.CSA</t>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.IPA/wiki/Parallelization-Mode</t>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0 (Default = 10%) You may skip this parameter when the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0 (Default = 10%) You may skip this parameter when the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA0005</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>≥ 0 (Default = 10%) You may skip this parameter when the reference spreadsheet is provided (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CSA0006</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Intensity height threshold for chromatographic peaks of MS level 2 EIC</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.msp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> files for Data-Independent Acquisition (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">) methods such as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SWATH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS^E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>, and All-Ion Fragmentation (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>AIF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>) analyses</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>"YES" OR "NO", When "YES", fill out the `</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DIA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">` tab. IDSL.CSA automatically detect </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>SWATH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>AIF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> data.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Select </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> to ignore precursor m/z. We suggest using a mass error for precursors in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>DDA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MS^E/SWATH-MS/AIF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> analyses and skipping this parameter for only one MS level analyses such as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CSA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>EI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>in-source fragmentation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.CSA/wiki/CSA-analysis-by-IDSL.CSA#csa-msp-generation</t>
-  </si>
-  <si>
-    <t>https://github.com/idslme/IDSL.CSA/wiki/CSA-analysis-by-IDSL.CSA#csa-aggregation-on-the-aligned-table</t>
-  </si>
-  <si>
-    <t>Create unique spectra by measuring pairwise similarity across entire samples</t>
-  </si>
-  <si>
-    <t>InChIKey14</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Default </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (= </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>FSDB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> index number) or any variable from the `</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>MetaVariables</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">` tab. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>InChIKey14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> performs the aggregation only based on the first 14 letters of the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>InChIKeys</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
+      <t>SpectraSimilarity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>` tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Retention time window (min) to group compounds with similar aggregation parameter (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AT0007</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) on the first column of the aligned MS/MS table annotation.</t>
+    </r>
+  </si>
+  <si>
+    <t>DIA0029</t>
+  </si>
+  <si>
+    <t>Retention time window (min) to find co-occurring peaks in individual IDSL.IPA peaklists</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4374,15 +4803,20 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <u/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4427,12 +4861,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FF6FD1D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DF8D8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4D3D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDA6CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -4649,14 +5101,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4776,7 +5339,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4885,27 +5448,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4918,27 +5460,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4963,9 +5484,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4974,9 +5492,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5007,30 +5522,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5129,6 +5620,186 @@
     <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5139,75 +5810,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5262,6 +5864,16 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF6FD1D7"/>
+      <color rgb="FFB4D3D9"/>
+      <color rgb="FF5DF8D8"/>
+      <color rgb="FFBDA6CE"/>
+      <color rgb="FF3B7597"/>
+      <color rgb="FF093C5D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -5535,18 +6147,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="72.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="3" max="3" width="72.7265625" style="2" customWidth="1"/>
     <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="5" width="70.42578125" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -5563,27 +6175,27 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="164" t="s">
-        <v>214</v>
+    <row r="2" spans="1:5" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="200" t="s">
+        <v>212</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="164"/>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="200"/>
       <c r="B3" s="71" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>103</v>
@@ -5592,78 +6204,78 @@
         <v>44</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="164"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="37.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="200"/>
       <c r="B4" s="71" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="164"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="200"/>
       <c r="B5" s="71" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="164"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="200"/>
       <c r="B6" s="71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>44</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="164"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="51.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="200"/>
       <c r="B7" s="78" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="165" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="201" t="s">
         <v>99</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D8" s="73" t="str">
         <f>CONCATENATE(FSDB!D4, "/", FSDB!D5, ".Rdata")</f>
@@ -5673,29 +6285,29 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="166"/>
+    <row r="9" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="202"/>
       <c r="B9" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D9" s="9" t="str">
         <f>CONCATENATE(CSA!D12, "/CSA_MSP")</f>
         <v>/path/to/folder//CSA_MSP</v>
       </c>
       <c r="E9" s="75" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="167"/>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="203"/>
       <c r="B10" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D10" s="77" t="str">
         <f>CSA!D12</f>
@@ -5706,23 +6318,23 @@
         <v>Do not fill when any of PARAM0001-PARAM0003 are selected "YES"</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C12"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C13"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C14"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C15"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C16"/>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C17"/>
     </row>
   </sheetData>
@@ -5737,20 +6349,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" style="45" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" style="45" customWidth="1"/>
-    <col min="3" max="3" width="75.140625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="50.28515625" style="45" customWidth="1"/>
-    <col min="5" max="5" width="77.42578125" style="45" customWidth="1"/>
-    <col min="6" max="6" width="41.7109375" style="45" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="45"/>
+    <col min="1" max="1" width="37.26953125" style="45" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" style="45" customWidth="1"/>
+    <col min="3" max="3" width="75.1796875" style="57" customWidth="1"/>
+    <col min="4" max="4" width="50.26953125" style="45" customWidth="1"/>
+    <col min="5" max="5" width="77.453125" style="45" customWidth="1"/>
+    <col min="6" max="6" width="41.7265625" style="45" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -5767,130 +6379,130 @@
         <v>4</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="41" customFormat="1" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
-        <v>368</v>
-      </c>
-      <c r="B2" s="87" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="41" customFormat="1" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="176" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="81" t="s">
+        <v>378</v>
+      </c>
+      <c r="F2" s="133"/>
+    </row>
+    <row r="3" spans="1:6" s="41" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="177"/>
+      <c r="B3" s="118" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="88" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="87" t="s">
+      <c r="C3" s="119" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E3" s="119" t="s">
         <v>408</v>
       </c>
-      <c r="F2" s="157"/>
-    </row>
-    <row r="3" spans="1:6" s="41" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="174"/>
-      <c r="B3" s="142" t="s">
+      <c r="F3" s="134"/>
+    </row>
+    <row r="4" spans="1:6" s="41" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="177"/>
+      <c r="B4" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="143" t="s">
-        <v>357</v>
-      </c>
-      <c r="D3" s="142" t="s">
+      <c r="C4" s="119" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="143" t="s">
-        <v>362</v>
-      </c>
-      <c r="F3" s="158"/>
-    </row>
-    <row r="4" spans="1:6" s="41" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="174"/>
-      <c r="B4" s="142" t="s">
+      <c r="E4" s="119" t="s">
+        <v>409</v>
+      </c>
+      <c r="F4" s="134"/>
+    </row>
+    <row r="5" spans="1:6" s="41" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="178"/>
+      <c r="B5" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="143" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="142" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="143" t="s">
-        <v>379</v>
-      </c>
-      <c r="F4" s="158"/>
-    </row>
-    <row r="5" spans="1:6" s="41" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="175"/>
-      <c r="B5" s="89" t="s">
+      <c r="C5" s="83" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" s="82">
+        <v>2</v>
+      </c>
+      <c r="E5" s="83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="135"/>
+    </row>
+    <row r="6" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="179" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="90" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" s="89">
-        <v>1</v>
-      </c>
-      <c r="E5" s="90" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="159"/>
-    </row>
-    <row r="6" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="176" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>178</v>
-      </c>
       <c r="C6" s="43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>100</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="160"/>
-    </row>
-    <row r="7" spans="1:6" s="41" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="177"/>
+      <c r="F6" s="136"/>
+    </row>
+    <row r="7" spans="1:6" s="41" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="180"/>
       <c r="B7" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="F7" s="136"/>
+    </row>
+    <row r="8" spans="1:6" s="41" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="180"/>
+      <c r="B8" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>354</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F7" s="160"/>
-    </row>
-    <row r="8" spans="1:6" s="41" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="177"/>
-      <c r="B8" s="44" t="s">
-        <v>180</v>
-      </c>
       <c r="C8" s="43" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D8" s="44" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="F8" s="161"/>
-    </row>
-    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="177"/>
+        <v>363</v>
+      </c>
+      <c r="F8" s="137"/>
+    </row>
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="180"/>
       <c r="B9" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D9" s="44" t="s">
         <v>39</v>
@@ -5898,31 +6510,31 @@
       <c r="E9" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="161"/>
-    </row>
-    <row r="10" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177"/>
+      <c r="F9" s="137"/>
+    </row>
+    <row r="10" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="180"/>
       <c r="B10" s="44" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="F10" s="161"/>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177"/>
+        <v>351</v>
+      </c>
+      <c r="F10" s="137"/>
+    </row>
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="180"/>
       <c r="B11" s="44" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>44</v>
@@ -5930,80 +6542,80 @@
       <c r="E11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="162"/>
-    </row>
-    <row r="12" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="178"/>
+      <c r="F11" s="138"/>
+    </row>
+    <row r="12" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="181"/>
       <c r="B12" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="C12" s="98" t="s">
-        <v>415</v>
+        <v>295</v>
+      </c>
+      <c r="C12" s="84" t="s">
+        <v>385</v>
       </c>
       <c r="D12" s="50" t="s">
         <v>100</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="163"/>
-    </row>
-    <row r="13" spans="1:6" ht="73.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="179" t="s">
-        <v>319</v>
+        <v>181</v>
+      </c>
+      <c r="F12" s="139"/>
+    </row>
+    <row r="13" spans="1:6" ht="73.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="182" t="s">
+        <v>312</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="E13" s="141" t="s">
-        <v>363</v>
-      </c>
-      <c r="F13" s="181" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="179"/>
+        <v>271</v>
+      </c>
+      <c r="E13" s="117" t="s">
+        <v>347</v>
+      </c>
+      <c r="F13" s="184" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="182"/>
       <c r="B14" s="18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="D14" s="18">
         <v>0.01</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="F14" s="181"/>
-    </row>
-    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="179"/>
+        <v>209</v>
+      </c>
+      <c r="F14" s="184"/>
+    </row>
+    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="182"/>
       <c r="B15" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="18">
         <v>5</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="F15" s="181"/>
-    </row>
-    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="179"/>
+        <v>162</v>
+      </c>
+      <c r="F15" s="184"/>
+    </row>
+    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="182"/>
       <c r="B16" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>7</v>
@@ -6014,12 +6626,12 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="181"/>
-    </row>
-    <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="179"/>
+      <c r="F16" s="184"/>
+    </row>
+    <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="182"/>
       <c r="B17" s="66" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>6</v>
@@ -6030,15 +6642,15 @@
       <c r="E17" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="181"/>
-    </row>
-    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="179"/>
+      <c r="F17" s="184"/>
+    </row>
+    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="182"/>
       <c r="B18" s="66" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D18" s="66">
         <v>250</v>
@@ -6046,47 +6658,47 @@
       <c r="E18" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="181"/>
-    </row>
-    <row r="19" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="179"/>
+      <c r="F18" s="184"/>
+    </row>
+    <row r="19" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="182"/>
       <c r="B19" s="38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="38">
         <v>2000</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F19" s="181"/>
-    </row>
-    <row r="20" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="179"/>
+        <v>243</v>
+      </c>
+      <c r="F19" s="184"/>
+    </row>
+    <row r="20" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="182"/>
       <c r="B20" s="38" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D20" s="38">
         <v>100</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="181"/>
-    </row>
-    <row r="21" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="179"/>
+        <v>149</v>
+      </c>
+      <c r="F20" s="184"/>
+    </row>
+    <row r="21" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="182"/>
       <c r="B21" s="38" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D21" s="66">
         <v>0</v>
@@ -6094,28 +6706,28 @@
       <c r="E21" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="181"/>
-    </row>
-    <row r="22" spans="1:6" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="179"/>
+      <c r="F21" s="184"/>
+    </row>
+    <row r="22" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="182"/>
       <c r="B22" s="38" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D22" s="66">
         <v>2</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="F22" s="181"/>
-    </row>
-    <row r="23" spans="1:6" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="180"/>
+        <v>162</v>
+      </c>
+      <c r="F22" s="184"/>
+    </row>
+    <row r="23" spans="1:6" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="183"/>
       <c r="B23" s="68" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>43</v>
@@ -6126,306 +6738,344 @@
       <c r="E23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="182"/>
-    </row>
-    <row r="24" spans="1:6" ht="31.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="183" t="s">
+      <c r="F23" s="185"/>
+    </row>
+    <row r="24" spans="1:6" ht="42.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="186" t="s">
+        <v>393</v>
+      </c>
+      <c r="B24" s="190" t="s">
+        <v>424</v>
+      </c>
+      <c r="C24" s="191"/>
+      <c r="D24" s="191"/>
+      <c r="E24" s="192"/>
+      <c r="F24" s="193" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="187"/>
+      <c r="B25" s="169" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="162" t="s">
+        <v>364</v>
+      </c>
+      <c r="D25" s="163" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="170" t="s">
+        <v>365</v>
+      </c>
+      <c r="F25" s="194"/>
+    </row>
+    <row r="26" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="187"/>
+      <c r="B26" s="197" t="s">
         <v>427</v>
       </c>
-      <c r="B24" s="126" t="s">
+      <c r="C26" s="198"/>
+      <c r="D26" s="198"/>
+      <c r="E26" s="199"/>
+      <c r="F26" s="194"/>
+    </row>
+    <row r="27" spans="1:6" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="187"/>
+      <c r="B27" s="165" t="s">
+        <v>220</v>
+      </c>
+      <c r="C27" s="166" t="s">
+        <v>416</v>
+      </c>
+      <c r="D27" s="167">
+        <v>10</v>
+      </c>
+      <c r="E27" s="168" t="s">
+        <v>403</v>
+      </c>
+      <c r="F27" s="194"/>
+    </row>
+    <row r="28" spans="1:6" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="188"/>
+      <c r="B28" s="141" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="127" t="s">
-        <v>381</v>
-      </c>
-      <c r="D24" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="127" t="s">
-        <v>382</v>
-      </c>
-      <c r="F24" s="186" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="184"/>
-      <c r="B25" s="129" t="s">
+      <c r="C28" s="142" t="s">
+        <v>343</v>
+      </c>
+      <c r="D28" s="141" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="195"/>
+    </row>
+    <row r="29" spans="1:6" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="188"/>
+      <c r="B29" s="164" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="128" t="s">
-        <v>358</v>
-      </c>
-      <c r="D25" s="129" t="s">
+      <c r="C29" s="140" t="s">
+        <v>321</v>
+      </c>
+      <c r="D29" s="164">
+        <v>0.05</v>
+      </c>
+      <c r="E29" s="140" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="195"/>
+    </row>
+    <row r="30" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="188"/>
+      <c r="B30" s="141" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="142" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" s="143" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="144" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="195"/>
+    </row>
+    <row r="31" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="188"/>
+      <c r="B31" s="141" t="s">
+        <v>229</v>
+      </c>
+      <c r="C31" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="143">
+        <v>1</v>
+      </c>
+      <c r="E31" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="195"/>
+    </row>
+    <row r="32" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="188"/>
+      <c r="B32" s="141" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" s="144" t="s">
+        <v>398</v>
+      </c>
+      <c r="D32" s="143">
+        <v>0.75</v>
+      </c>
+      <c r="E32" s="144" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="195"/>
+    </row>
+    <row r="33" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="189"/>
+      <c r="B33" s="145" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="146" t="s">
+        <v>399</v>
+      </c>
+      <c r="D33" s="145">
+        <v>0.75</v>
+      </c>
+      <c r="E33" s="146" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" s="196"/>
+    </row>
+    <row r="34" spans="1:6" ht="23.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="171" t="s">
+        <v>223</v>
+      </c>
+      <c r="B34" s="147" t="s">
+        <v>238</v>
+      </c>
+      <c r="C34" s="148" t="s">
+        <v>327</v>
+      </c>
+      <c r="D34" s="147">
+        <v>0.05</v>
+      </c>
+      <c r="E34" s="149" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="173" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" s="57" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="171"/>
+      <c r="B35" s="150" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="151" t="s">
+        <v>317</v>
+      </c>
+      <c r="D35" s="150">
+        <v>5</v>
+      </c>
+      <c r="E35" s="152" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" s="174"/>
+    </row>
+    <row r="36" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="171"/>
+      <c r="B36" s="150" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="151" t="s">
+        <v>328</v>
+      </c>
+      <c r="D36" s="153">
+        <v>3</v>
+      </c>
+      <c r="E36" s="154" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="174"/>
+    </row>
+    <row r="37" spans="1:6" ht="23.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="171"/>
+      <c r="B37" s="150" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37" s="151" t="s">
+        <v>329</v>
+      </c>
+      <c r="D37" s="153">
+        <v>0.1</v>
+      </c>
+      <c r="E37" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="174"/>
+    </row>
+    <row r="38" spans="1:6" ht="97.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="171"/>
+      <c r="B38" s="150" t="s">
+        <v>307</v>
+      </c>
+      <c r="C38" s="151" t="s">
+        <v>330</v>
+      </c>
+      <c r="D38" s="153">
+        <v>0.5</v>
+      </c>
+      <c r="E38" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="174"/>
+    </row>
+    <row r="39" spans="1:6" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="171"/>
+      <c r="B39" s="150" t="s">
+        <v>308</v>
+      </c>
+      <c r="C39" s="148" t="s">
+        <v>346</v>
+      </c>
+      <c r="D39" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="128" t="s">
+      <c r="E39" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="187"/>
-    </row>
-    <row r="26" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="184"/>
-      <c r="B26" s="129" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="128" t="s">
-        <v>329</v>
-      </c>
-      <c r="D26" s="129">
+      <c r="F39" s="174"/>
+    </row>
+    <row r="40" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="171"/>
+      <c r="B40" s="150" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" s="148" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="153">
         <f>D17</f>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E26" s="128" t="s">
-        <v>383</v>
-      </c>
-      <c r="F26" s="187"/>
-    </row>
-    <row r="27" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="184"/>
-      <c r="B27" s="129" t="s">
-        <v>224</v>
-      </c>
-      <c r="C27" s="128" t="s">
-        <v>328</v>
-      </c>
-      <c r="D27" s="129">
-        <v>0.05</v>
-      </c>
-      <c r="E27" s="128" t="s">
-        <v>384</v>
-      </c>
-      <c r="F27" s="187"/>
-    </row>
-    <row r="28" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="184"/>
-      <c r="B28" s="129" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="128" t="s">
-        <v>343</v>
-      </c>
-      <c r="D28" s="129">
-        <v>10</v>
-      </c>
-      <c r="E28" s="128" t="s">
-        <v>420</v>
-      </c>
-      <c r="F28" s="187"/>
-    </row>
-    <row r="29" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="184"/>
-      <c r="B29" s="129" t="s">
-        <v>231</v>
-      </c>
-      <c r="C29" s="128" t="s">
-        <v>307</v>
-      </c>
-      <c r="D29" s="122" t="b">
+      <c r="E40" s="155" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="174"/>
+    </row>
+    <row r="41" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="171"/>
+      <c r="B41" s="150" t="s">
+        <v>344</v>
+      </c>
+      <c r="C41" s="156" t="s">
+        <v>300</v>
+      </c>
+      <c r="D41" s="153" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="123" t="s">
+      <c r="E41" s="155" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="187"/>
-    </row>
-    <row r="30" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="185"/>
-      <c r="B30" s="124" t="s">
-        <v>232</v>
-      </c>
-      <c r="C30" s="125" t="s">
-        <v>249</v>
-      </c>
-      <c r="D30" s="124">
-        <v>0.9</v>
-      </c>
-      <c r="E30" s="125" t="s">
+      <c r="F41" s="174"/>
+    </row>
+    <row r="42" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="171"/>
+      <c r="B42" s="150" t="s">
+        <v>345</v>
+      </c>
+      <c r="C42" s="157" t="s">
+        <v>233</v>
+      </c>
+      <c r="D42" s="158">
+        <v>0.6</v>
+      </c>
+      <c r="E42" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="F30" s="188"/>
-    </row>
-    <row r="31" spans="1:6" ht="23.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="168" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="80" t="s">
-        <v>234</v>
-      </c>
-      <c r="C31" s="95" t="s">
-        <v>337</v>
-      </c>
-      <c r="D31" s="80">
-        <v>0.05</v>
-      </c>
-      <c r="E31" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="F31" s="170" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" s="57" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="168"/>
-      <c r="B32" s="82" t="s">
-        <v>240</v>
-      </c>
-      <c r="C32" s="92" t="s">
-        <v>324</v>
-      </c>
-      <c r="D32" s="82">
-        <v>5</v>
-      </c>
-      <c r="E32" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" s="171"/>
-    </row>
-    <row r="33" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="168"/>
-      <c r="B33" s="84" t="s">
-        <v>244</v>
-      </c>
-      <c r="C33" s="92" t="s">
-        <v>338</v>
-      </c>
-      <c r="D33" s="84">
-        <v>3</v>
-      </c>
-      <c r="E33" s="85" t="s">
-        <v>163</v>
-      </c>
-      <c r="F33" s="171"/>
-    </row>
-    <row r="34" spans="1:6" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="168"/>
-      <c r="B34" s="84" t="s">
-        <v>252</v>
-      </c>
-      <c r="C34" s="92" t="s">
-        <v>339</v>
-      </c>
-      <c r="D34" s="84">
-        <v>0.1</v>
-      </c>
-      <c r="E34" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="171"/>
-    </row>
-    <row r="35" spans="1:6" ht="97.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="168"/>
-      <c r="B35" s="84" t="s">
-        <v>253</v>
-      </c>
-      <c r="C35" s="92" t="s">
-        <v>340</v>
-      </c>
-      <c r="D35" s="84">
-        <v>0.5</v>
-      </c>
-      <c r="E35" s="85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="171"/>
-    </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="168"/>
-      <c r="B36" s="84" t="s">
-        <v>314</v>
-      </c>
-      <c r="C36" s="95" t="s">
-        <v>361</v>
-      </c>
-      <c r="D36" s="84" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" s="91" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="171"/>
-    </row>
-    <row r="37" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="168"/>
-      <c r="B37" s="84" t="s">
-        <v>315</v>
-      </c>
-      <c r="C37" s="95" t="s">
-        <v>241</v>
-      </c>
-      <c r="D37" s="84">
-        <f>D17</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="E37" s="91" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="171"/>
-    </row>
-    <row r="38" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="168"/>
-      <c r="B38" s="84" t="s">
-        <v>320</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="D38" s="84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="91" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="171"/>
-    </row>
-    <row r="39" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="168"/>
-      <c r="B39" s="96" t="s">
-        <v>359</v>
-      </c>
-      <c r="C39" s="97" t="s">
+      <c r="F42" s="174"/>
+    </row>
+    <row r="43" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="172"/>
+      <c r="B43" s="159" t="s">
+        <v>400</v>
+      </c>
+      <c r="C43" s="160" t="s">
+        <v>304</v>
+      </c>
+      <c r="D43" s="159" t="s">
         <v>235</v>
       </c>
-      <c r="D39" s="96">
-        <v>0.6</v>
-      </c>
-      <c r="E39" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="171"/>
-    </row>
-    <row r="40" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="169"/>
-      <c r="B40" s="93" t="s">
-        <v>360</v>
-      </c>
-      <c r="C40" s="94" t="s">
-        <v>311</v>
-      </c>
-      <c r="D40" s="93" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" s="86" t="s">
-        <v>325</v>
-      </c>
-      <c r="F40" s="172"/>
-    </row>
-    <row r="41" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="E43" s="161" t="s">
+        <v>318</v>
+      </c>
+      <c r="F43" s="175"/>
+    </row>
+    <row r="44" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A31:A40"/>
-    <mergeCell ref="F31:F40"/>
+  <mergeCells count="10">
+    <mergeCell ref="A34:A43"/>
+    <mergeCell ref="F34:F43"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A12"/>
     <mergeCell ref="A13:A23"/>
     <mergeCell ref="F13:F23"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="F24:F30"/>
+    <mergeCell ref="A24:A33"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:F33"/>
+    <mergeCell ref="B26:E26"/>
   </mergeCells>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F13" r:id="rId1" location="csa-msp-generation"/>
-    <hyperlink ref="F24" r:id="rId2"/>
-    <hyperlink ref="F31" r:id="rId3" location="csa-aggregation-on-the-aligned-table"/>
+    <hyperlink ref="F13" r:id="rId1" location="csa-msp-generation" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="F24" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="F34" r:id="rId3" location="csa-aggregation-on-the-aligned-table" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -6433,20 +7083,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" style="45" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="45" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" style="45" customWidth="1"/>
     <col min="3" max="3" width="76" style="57" customWidth="1"/>
-    <col min="4" max="4" width="50.28515625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="50.26953125" style="45" customWidth="1"/>
     <col min="5" max="5" width="78" style="45" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" style="45" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="45"/>
+    <col min="6" max="6" width="42.08984375" style="45" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -6459,153 +7109,153 @@
       <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="106" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
-        <v>369</v>
-      </c>
-      <c r="B2" s="87" t="s">
+      <c r="F1" s="16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="176" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="88" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="87" t="s">
+      <c r="C2" s="81" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="88" t="s">
-        <v>406</v>
-      </c>
-      <c r="F2" s="138"/>
-    </row>
-    <row r="3" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="174"/>
-      <c r="B3" s="136" t="s">
+      <c r="E2" s="81" t="s">
+        <v>377</v>
+      </c>
+      <c r="F2" s="114"/>
+    </row>
+    <row r="3" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="177"/>
+      <c r="B3" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="D3" s="136" t="s">
+      <c r="C3" s="113" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="137" t="s">
+      <c r="E3" s="113" t="s">
         <v>407</v>
       </c>
-      <c r="F3" s="144"/>
-    </row>
-    <row r="4" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="175"/>
-      <c r="B4" s="89" t="s">
+      <c r="F3" s="120"/>
+    </row>
+    <row r="4" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="178"/>
+      <c r="B4" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="89">
+      <c r="D4" s="82">
         <f>CSA!D5</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="139"/>
-    </row>
-    <row r="5" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="176" t="s">
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="179" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="79" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="69" t="str">
         <f>CSA!D6</f>
         <v>/path/to/folder/</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="111"/>
-    </row>
-    <row r="6" spans="1:6" s="41" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="177"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="95"/>
+    </row>
+    <row r="6" spans="1:6" s="41" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="180"/>
       <c r="B6" s="79" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>355</v>
+        <v>422</v>
       </c>
       <c r="D6" s="44" t="str">
         <f>CSA!D7</f>
         <v>NA</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F6" s="111"/>
-    </row>
-    <row r="7" spans="1:6" s="41" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="177"/>
+        <v>380</v>
+      </c>
+      <c r="F6" s="95"/>
+    </row>
+    <row r="7" spans="1:6" s="41" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="180"/>
       <c r="B7" s="42" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D7" s="44" t="str">
         <f>CSA!D8</f>
         <v>All</v>
       </c>
-      <c r="E7" s="101" t="s">
-        <v>385</v>
-      </c>
-      <c r="F7" s="112"/>
-    </row>
-    <row r="8" spans="1:6" s="41" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="177"/>
+      <c r="E7" s="87" t="s">
+        <v>366</v>
+      </c>
+      <c r="F7" s="96"/>
+    </row>
+    <row r="8" spans="1:6" s="41" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="180"/>
       <c r="B8" s="42" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D8" s="44" t="str">
         <f>CSA!D9</f>
         <v>/peaklists</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="112"/>
-    </row>
-    <row r="9" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="177"/>
+      <c r="F8" s="96"/>
+    </row>
+    <row r="9" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="180"/>
       <c r="B9" s="42" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D9" s="44" t="str">
         <f>CSA!D10</f>
         <v>/peak_alignment</v>
       </c>
-      <c r="E9" s="101" t="s">
-        <v>349</v>
-      </c>
-      <c r="F9" s="113"/>
-    </row>
-    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177"/>
+      <c r="E9" s="87" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="97"/>
+    </row>
+    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="180"/>
       <c r="B10" s="42" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>42</v>
@@ -6613,66 +7263,67 @@
       <c r="D10" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="102" t="s">
-        <v>386</v>
-      </c>
-      <c r="F10" s="113"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177"/>
+      <c r="E10" s="88" t="s">
+        <v>410</v>
+      </c>
+      <c r="F10" s="97"/>
+    </row>
+    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="180"/>
       <c r="B11" s="42" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C11" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="102" t="s">
+      <c r="D11" s="47" t="str">
+        <f>CSA!D11</f>
+        <v>NO</v>
+      </c>
+      <c r="E11" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="113"/>
-    </row>
-    <row r="12" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="178"/>
+      <c r="F11" s="97"/>
+    </row>
+    <row r="12" spans="1:6" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="181"/>
       <c r="B12" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="98" t="s">
-        <v>413</v>
+      <c r="C12" s="84" t="s">
+        <v>383</v>
       </c>
       <c r="D12" s="50" t="str">
         <f>CSA!D12</f>
         <v>/path/to/folder/</v>
       </c>
-      <c r="E12" s="103" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="114"/>
-    </row>
-    <row r="13" spans="1:6" ht="29.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
-        <v>213</v>
-      </c>
-      <c r="B13" s="130" t="s">
+      <c r="E12" s="89" t="s">
+        <v>404</v>
+      </c>
+      <c r="F12" s="98"/>
+    </row>
+    <row r="13" spans="1:6" ht="29.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="204" t="s">
+        <v>211</v>
+      </c>
+      <c r="B13" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="132" t="s">
-        <v>312</v>
-      </c>
-      <c r="E13" s="133" t="s">
-        <v>313</v>
-      </c>
-      <c r="F13" s="156" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="D13" s="108" t="s">
+        <v>305</v>
+      </c>
+      <c r="E13" s="109" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="132" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="204"/>
       <c r="B14" s="53" t="s">
         <v>52</v>
       </c>
@@ -6685,78 +7336,78 @@
       <c r="E14" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="193" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="191"/>
+      <c r="F14" s="206" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="204"/>
       <c r="B15" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>420</v>
+      </c>
+      <c r="E15" s="90" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" s="207"/>
+    </row>
+    <row r="16" spans="1:6" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="204"/>
+      <c r="B16" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="104" t="s">
-        <v>370</v>
-      </c>
-      <c r="F15" s="194"/>
-    </row>
-    <row r="16" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
-      <c r="B16" s="53" t="s">
-        <v>145</v>
-      </c>
       <c r="C16" s="54" t="s">
-        <v>186</v>
+        <v>421</v>
       </c>
       <c r="D16" s="53">
-        <v>0.01</v>
-      </c>
-      <c r="E16" s="105" t="s">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="E16" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="194"/>
-    </row>
-    <row r="17" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="F16" s="207"/>
+    </row>
+    <row r="17" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="204"/>
       <c r="B17" s="53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D17" s="53">
         <v>10</v>
       </c>
-      <c r="E17" s="105" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" s="194"/>
-    </row>
-    <row r="18" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="E17" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="F17" s="207"/>
+    </row>
+    <row r="18" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="204"/>
       <c r="B18" s="53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D18" s="53">
         <v>10</v>
       </c>
-      <c r="E18" s="105" t="s">
-        <v>170</v>
-      </c>
-      <c r="F18" s="194"/>
-    </row>
-    <row r="19" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
+      <c r="E18" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="207"/>
+    </row>
+    <row r="19" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="205"/>
       <c r="B19" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C19" s="56" t="s">
         <v>43</v>
@@ -6765,161 +7416,208 @@
         <v>0.85</v>
       </c>
       <c r="E19" s="56" t="s">
-        <v>169</v>
-      </c>
-      <c r="F19" s="195"/>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="183" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="208"/>
+    </row>
+    <row r="20" spans="1:6" ht="41" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="186" t="s">
+        <v>393</v>
+      </c>
+      <c r="B20" s="190" t="s">
+        <v>425</v>
+      </c>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="193" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="187"/>
+      <c r="B21" s="169" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="162" t="s">
+        <v>411</v>
+      </c>
+      <c r="D21" s="163" t="str">
+        <f>CSA!D25</f>
+        <v>Name</v>
+      </c>
+      <c r="E21" s="170" t="s">
+        <v>406</v>
+      </c>
+      <c r="F21" s="194"/>
+    </row>
+    <row r="22" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="187"/>
+      <c r="B22" s="197" t="s">
         <v>427</v>
       </c>
-      <c r="B20" s="126" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="127" t="s">
-        <v>387</v>
-      </c>
-      <c r="D20" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="127" t="s">
-        <v>388</v>
-      </c>
-      <c r="F20" s="186" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="184"/>
-      <c r="B21" s="129" t="s">
-        <v>254</v>
-      </c>
-      <c r="C21" s="128" t="s">
-        <v>358</v>
-      </c>
-      <c r="D21" s="129" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="128" t="s">
+      <c r="C22" s="198"/>
+      <c r="D22" s="198"/>
+      <c r="E22" s="199"/>
+      <c r="F22" s="194"/>
+    </row>
+    <row r="23" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="187"/>
+      <c r="B23" s="165" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="166" t="s">
+        <v>415</v>
+      </c>
+      <c r="D23" s="167">
+        <f>CSA!D27</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="168" t="s">
+        <v>403</v>
+      </c>
+      <c r="F23" s="194"/>
+    </row>
+    <row r="24" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="188"/>
+      <c r="B24" s="141" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" s="142" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="141" t="str">
+        <f>CSA!D28</f>
+        <v>NO</v>
+      </c>
+      <c r="E24" s="142" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="189"/>
-    </row>
-    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="184"/>
-      <c r="B22" s="129" t="s">
-        <v>321</v>
-      </c>
-      <c r="C22" s="128" t="s">
-        <v>333</v>
-      </c>
-      <c r="D22" s="129">
-        <f>D14</f>
-        <v>0.01</v>
-      </c>
-      <c r="E22" s="128" t="s">
-        <v>389</v>
-      </c>
-      <c r="F22" s="189"/>
-    </row>
-    <row r="23" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="184"/>
-      <c r="B23" s="129" t="s">
-        <v>346</v>
-      </c>
-      <c r="C23" s="128" t="s">
-        <v>330</v>
-      </c>
-      <c r="D23" s="122">
+      <c r="F24" s="195"/>
+    </row>
+    <row r="25" spans="1:6" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="188"/>
+      <c r="B25" s="164" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="140" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="141">
+        <f>CSA!D29</f>
         <v>0.05</v>
       </c>
-      <c r="E23" s="123" t="s">
-        <v>390</v>
-      </c>
-      <c r="F23" s="189"/>
-    </row>
-    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="184"/>
-      <c r="B24" s="129" t="s">
-        <v>364</v>
-      </c>
-      <c r="C24" s="128" t="s">
-        <v>344</v>
-      </c>
-      <c r="D24" s="129">
-        <v>10</v>
-      </c>
-      <c r="E24" s="128" t="s">
-        <v>419</v>
-      </c>
-      <c r="F24" s="189"/>
-    </row>
-    <row r="25" spans="1:6" ht="45.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="184"/>
-      <c r="B25" s="129" t="s">
-        <v>365</v>
-      </c>
-      <c r="C25" s="128" t="s">
-        <v>307</v>
-      </c>
-      <c r="D25" s="122" t="b">
+      <c r="E25" s="140" t="s">
+        <v>417</v>
+      </c>
+      <c r="F25" s="195"/>
+    </row>
+    <row r="26" spans="1:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="188"/>
+      <c r="B26" s="164" t="s">
+        <v>348</v>
+      </c>
+      <c r="C26" s="142" t="s">
+        <v>300</v>
+      </c>
+      <c r="D26" s="141" t="b">
+        <f>CSA!D30</f>
         <v>1</v>
       </c>
-      <c r="E25" s="123" t="s">
+      <c r="E26" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="189"/>
-    </row>
-    <row r="26" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="185"/>
-      <c r="B26" s="124" t="s">
-        <v>366</v>
-      </c>
-      <c r="C26" s="125" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26" s="124">
-        <v>0.9</v>
-      </c>
-      <c r="E26" s="125" t="s">
+      <c r="F26" s="195"/>
+    </row>
+    <row r="27" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+      <c r="A27" s="188"/>
+      <c r="B27" s="164" t="s">
+        <v>349</v>
+      </c>
+      <c r="C27" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="141">
+        <f>CSA!D31</f>
+        <v>1</v>
+      </c>
+      <c r="E27" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="195"/>
+    </row>
+    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="188"/>
+      <c r="B28" s="164" t="s">
+        <v>350</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>398</v>
+      </c>
+      <c r="D28" s="141">
+        <f>CSA!D32</f>
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="190"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="F28" s="195"/>
+    </row>
+    <row r="29" spans="1:6" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="189"/>
+      <c r="B29" s="145" t="s">
+        <v>405</v>
+      </c>
+      <c r="C29" s="146" t="s">
+        <v>399</v>
+      </c>
+      <c r="D29" s="145">
+        <f>CSA!D33</f>
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="146" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" s="196"/>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A5:A12"/>
+  <mergeCells count="8">
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="F20:F26"/>
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="F14:F19"/>
+    <mergeCell ref="A20:A29"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:F29"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A5:A12"/>
   </mergeCells>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F20" r:id="rId1"/>
-    <hyperlink ref="F13" r:id="rId2"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="F20" r:id="rId2" xr:uid="{67C23546-7E49-43E2-B17B-DE8247B534DE}"/>
+    <hyperlink ref="F14" r:id="rId3" xr:uid="{47758DAB-7A83-4087-A16E-A586AF7BF21E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" style="45" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="45" customWidth="1"/>
-    <col min="3" max="3" width="75.5703125" style="57" customWidth="1"/>
-    <col min="4" max="4" width="50.28515625" style="45" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" style="45" customWidth="1"/>
+    <col min="3" max="3" width="75.54296875" style="57" customWidth="1"/>
+    <col min="4" max="4" width="50.26953125" style="45" customWidth="1"/>
     <col min="5" max="5" width="78" style="45" customWidth="1"/>
-    <col min="6" max="6" width="41.5703125" style="45" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="45"/>
+    <col min="6" max="6" width="41.54296875" style="45" customWidth="1"/>
+    <col min="7" max="16384" width="9.1796875" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="41" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -6932,240 +7630,242 @@
       <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="106" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="173" t="s">
-        <v>371</v>
-      </c>
-      <c r="B2" s="87" t="s">
+      <c r="F1" s="16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="176" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="88" t="s">
-        <v>228</v>
-      </c>
-      <c r="D2" s="87" t="s">
+      <c r="C2" s="81" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="88" t="s">
-        <v>404</v>
-      </c>
-      <c r="F2" s="138"/>
-    </row>
-    <row r="3" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="174"/>
-      <c r="B3" s="136" t="s">
+      <c r="E2" s="81" t="s">
+        <v>375</v>
+      </c>
+      <c r="F2" s="114"/>
+    </row>
+    <row r="3" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="177"/>
+      <c r="B3" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="D3" s="136" t="s">
+      <c r="C3" s="113" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="137" t="s">
-        <v>405</v>
-      </c>
-      <c r="F3" s="144"/>
-    </row>
-    <row r="4" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="175"/>
-      <c r="B4" s="89" t="s">
+      <c r="E3" s="113" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="120"/>
+    </row>
+    <row r="4" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="178"/>
+      <c r="B4" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="89">
+      <c r="D4" s="82">
         <f>DDA!D4</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="139"/>
-    </row>
-    <row r="5" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="176" t="s">
+      <c r="F4" s="115"/>
+    </row>
+    <row r="5" spans="1:6" s="41" customFormat="1" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="179" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="79" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="69" t="str">
-        <f>CSA!D6</f>
+        <f>DDA!D5</f>
         <v>/path/to/folder/</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="111"/>
-    </row>
-    <row r="6" spans="1:6" s="41" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="177"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="95"/>
+    </row>
+    <row r="6" spans="1:6" s="41" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="180"/>
       <c r="B6" s="79" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>356</v>
+        <v>423</v>
       </c>
       <c r="D6" s="44" t="str">
-        <f>CSA!D7</f>
+        <f>DDA!D6</f>
         <v>NA</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F6" s="111"/>
-    </row>
-    <row r="7" spans="1:6" s="41" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="177"/>
+        <v>380</v>
+      </c>
+      <c r="F6" s="95"/>
+    </row>
+    <row r="7" spans="1:6" s="41" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="180"/>
       <c r="B7" s="42" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D7" s="44" t="str">
-        <f>CSA!D8</f>
+        <f>DDA!D7</f>
         <v>All</v>
       </c>
-      <c r="E7" s="101" t="s">
-        <v>391</v>
-      </c>
-      <c r="F7" s="112"/>
-    </row>
-    <row r="8" spans="1:6" s="41" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="177"/>
+      <c r="E7" s="87" t="s">
+        <v>367</v>
+      </c>
+      <c r="F7" s="96"/>
+    </row>
+    <row r="8" spans="1:6" s="41" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="180"/>
       <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D8" s="44" t="str">
-        <f>CSA!D9</f>
+        <f>DDA!D8</f>
         <v>/peaklists</v>
       </c>
-      <c r="E8" s="101" t="s">
+      <c r="E8" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="112"/>
-    </row>
-    <row r="9" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="177"/>
+      <c r="F8" s="96"/>
+    </row>
+    <row r="9" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="180"/>
       <c r="B9" s="42" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D9" s="44" t="str">
-        <f>CSA!D10</f>
+        <f>DDA!D9</f>
         <v>/peak_alignment</v>
       </c>
-      <c r="E9" s="101" t="s">
-        <v>349</v>
-      </c>
-      <c r="F9" s="153"/>
-    </row>
-    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177"/>
+      <c r="E9" s="87" t="s">
+        <v>337</v>
+      </c>
+      <c r="F9" s="129"/>
+    </row>
+    <row r="10" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="180"/>
       <c r="B10" s="42" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="102" t="s">
-        <v>392</v>
-      </c>
-      <c r="F10" s="153"/>
-    </row>
-    <row r="11" spans="1:6" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177"/>
+      <c r="D10" s="47" t="str">
+        <f>DDA!D10</f>
+        <v>All</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="129"/>
+    </row>
+    <row r="11" spans="1:6" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="180"/>
       <c r="B11" s="42" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="102" t="s">
+        <v>280</v>
+      </c>
+      <c r="D11" s="47" t="str">
+        <f>DDA!D11</f>
+        <v>NO</v>
+      </c>
+      <c r="E11" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="153"/>
-    </row>
-    <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="178"/>
+      <c r="F11" s="129"/>
+    </row>
+    <row r="12" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="181"/>
       <c r="B12" s="48" t="s">
-        <v>372</v>
-      </c>
-      <c r="C12" s="98" t="s">
-        <v>414</v>
+        <v>356</v>
+      </c>
+      <c r="C12" s="84" t="s">
+        <v>384</v>
       </c>
       <c r="D12" s="50" t="str">
-        <f>CSA!D12</f>
+        <f>DDA!D12</f>
         <v>/path/to/folder/</v>
       </c>
-      <c r="E12" s="103" t="s">
-        <v>182</v>
-      </c>
-      <c r="F12" s="154"/>
-    </row>
-    <row r="13" spans="1:6" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="179" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="132" t="s">
+      <c r="E12" s="89" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="130"/>
+    </row>
+    <row r="13" spans="1:6" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="182" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="132" t="s">
-        <v>312</v>
-      </c>
-      <c r="E13" s="134" t="s">
-        <v>313</v>
-      </c>
-      <c r="F13" s="155" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="179"/>
+      <c r="D13" s="108" t="s">
+        <v>305</v>
+      </c>
+      <c r="E13" s="110" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13" s="131" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="182"/>
       <c r="B14" s="38" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="D14" s="140">
+        <v>388</v>
+      </c>
+      <c r="D14" s="116">
         <v>1000</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="196" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="179"/>
+      <c r="F14" s="209" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="182"/>
       <c r="B15" s="18" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>7</v>
@@ -7176,12 +7876,12 @@
       <c r="E15" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="181"/>
-    </row>
-    <row r="16" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="179"/>
+      <c r="F15" s="184"/>
+    </row>
+    <row r="16" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="182"/>
       <c r="B16" s="38" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>8</v>
@@ -7192,10 +7892,10 @@
       <c r="E16" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="181"/>
-    </row>
-    <row r="17" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="179"/>
+      <c r="F16" s="184"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="182"/>
       <c r="B17" s="66" t="s">
         <v>37</v>
       </c>
@@ -7208,15 +7908,15 @@
       <c r="E17" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="181"/>
-    </row>
-    <row r="18" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="179"/>
+      <c r="F17" s="184"/>
+    </row>
+    <row r="18" spans="1:6" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="182"/>
       <c r="B18" s="66" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D18" s="66">
         <v>50</v>
@@ -7224,15 +7924,15 @@
       <c r="E18" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="181"/>
-    </row>
-    <row r="19" spans="1:6" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="179"/>
+      <c r="F18" s="184"/>
+    </row>
+    <row r="19" spans="1:6" ht="51.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="182"/>
       <c r="B19" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="38">
         <v>100</v>
@@ -7240,28 +7940,28 @@
       <c r="E19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="181"/>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="179"/>
+      <c r="F19" s="184"/>
+    </row>
+    <row r="20" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="182"/>
       <c r="B20" s="38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D20" s="38">
         <v>90</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" s="181"/>
-    </row>
-    <row r="21" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="180"/>
+        <v>149</v>
+      </c>
+      <c r="F20" s="184"/>
+    </row>
+    <row r="21" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="183"/>
       <c r="B21" s="68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>43</v>
@@ -7272,138 +7972,184 @@
       <c r="E21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="182"/>
-    </row>
-    <row r="22" spans="1:6" ht="37.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="183" t="s">
+      <c r="F21" s="185"/>
+    </row>
+    <row r="22" spans="1:6" ht="37.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="186" t="s">
+        <v>393</v>
+      </c>
+      <c r="B22" s="190" t="s">
+        <v>426</v>
+      </c>
+      <c r="C22" s="191"/>
+      <c r="D22" s="191"/>
+      <c r="E22" s="192"/>
+      <c r="F22" s="193" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="187"/>
+      <c r="B23" s="169" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" s="162" t="s">
+        <v>413</v>
+      </c>
+      <c r="D23" s="163" t="str">
+        <f>DDA!D21</f>
+        <v>Name</v>
+      </c>
+      <c r="E23" s="170" t="s">
+        <v>414</v>
+      </c>
+      <c r="F23" s="194"/>
+    </row>
+    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="187"/>
+      <c r="B24" s="197" t="s">
         <v>427</v>
       </c>
-      <c r="B22" s="126" t="s">
-        <v>215</v>
-      </c>
-      <c r="C22" s="127" t="s">
-        <v>396</v>
-      </c>
-      <c r="D22" s="126" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="127" t="s">
-        <v>393</v>
-      </c>
-      <c r="F22" s="186" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="184"/>
-      <c r="B23" s="129" t="s">
-        <v>256</v>
-      </c>
-      <c r="C23" s="128" t="s">
+      <c r="C24" s="198"/>
+      <c r="D24" s="198"/>
+      <c r="E24" s="199"/>
+      <c r="F24" s="194"/>
+    </row>
+    <row r="25" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="187"/>
+      <c r="B25" s="165" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="166" t="s">
+        <v>332</v>
+      </c>
+      <c r="D25" s="167">
+        <f>DDA!D23</f>
+        <v>10</v>
+      </c>
+      <c r="E25" s="168" t="s">
+        <v>403</v>
+      </c>
+      <c r="F25" s="194"/>
+    </row>
+    <row r="26" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="188"/>
+      <c r="B26" s="141" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="142" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" s="141" t="str">
+        <f>DDA!D24</f>
+        <v>NO</v>
+      </c>
+      <c r="E26" s="142" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="195"/>
+    </row>
+    <row r="27" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="188"/>
+      <c r="B27" s="141" t="s">
+        <v>341</v>
+      </c>
+      <c r="C27" s="140" t="s">
+        <v>323</v>
+      </c>
+      <c r="D27" s="141">
+        <f>DDA!D25</f>
+        <v>0.05</v>
+      </c>
+      <c r="E27" s="140" t="s">
+        <v>419</v>
+      </c>
+      <c r="F27" s="195"/>
+    </row>
+    <row r="28" spans="1:6" ht="51.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="188"/>
+      <c r="B28" s="141" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28" s="142" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="141" t="b">
+        <f>DDA!D26</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="144" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="195"/>
+    </row>
+    <row r="29" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+      <c r="A29" s="188"/>
+      <c r="B29" s="141" t="s">
         <v>358</v>
       </c>
-      <c r="D23" s="129" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="189"/>
-    </row>
-    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="184"/>
-      <c r="B24" s="129" t="s">
-        <v>322</v>
-      </c>
-      <c r="C24" s="128" t="s">
-        <v>329</v>
-      </c>
-      <c r="D24" s="129">
-        <f>D17</f>
-        <v>0.01</v>
-      </c>
-      <c r="E24" s="128" t="s">
-        <v>394</v>
-      </c>
-      <c r="F24" s="189"/>
-    </row>
-    <row r="25" spans="1:6" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="184"/>
-      <c r="B25" s="129" t="s">
-        <v>353</v>
-      </c>
-      <c r="C25" s="128" t="s">
-        <v>331</v>
-      </c>
-      <c r="D25" s="122">
-        <v>0.05</v>
-      </c>
-      <c r="E25" s="123" t="s">
-        <v>395</v>
-      </c>
-      <c r="F25" s="189"/>
-    </row>
-    <row r="26" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="184"/>
-      <c r="B26" s="129" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26" s="128" t="s">
-        <v>342</v>
-      </c>
-      <c r="D26" s="129">
-        <v>10</v>
-      </c>
-      <c r="E26" s="128" t="s">
-        <v>418</v>
-      </c>
-      <c r="F26" s="189"/>
-    </row>
-    <row r="27" spans="1:6" ht="45.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="184"/>
-      <c r="B27" s="129" t="s">
-        <v>374</v>
-      </c>
-      <c r="C27" s="128" t="s">
-        <v>307</v>
-      </c>
-      <c r="D27" s="122" t="b">
+      <c r="C29" s="144" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="141">
+        <f>DDA!D27</f>
         <v>1</v>
       </c>
-      <c r="E27" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="189"/>
-    </row>
-    <row r="28" spans="1:6" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="185"/>
-      <c r="B28" s="124" t="s">
-        <v>375</v>
-      </c>
-      <c r="C28" s="125" t="s">
-        <v>257</v>
-      </c>
-      <c r="D28" s="124">
-        <v>0.9</v>
-      </c>
-      <c r="E28" s="125" t="s">
+      <c r="E29" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="195"/>
+    </row>
+    <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="188"/>
+      <c r="B30" s="141" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>398</v>
+      </c>
+      <c r="D30" s="141">
+        <f>DDA!D28</f>
+        <v>0.75</v>
+      </c>
+      <c r="E30" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="F28" s="190"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="F30" s="195"/>
+    </row>
+    <row r="31" spans="1:6" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="189"/>
+      <c r="B31" s="145" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" s="146" t="s">
+        <v>399</v>
+      </c>
+      <c r="D31" s="145">
+        <f>DDA!D29</f>
+        <v>0.75</v>
+      </c>
+      <c r="E31" s="146" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="196"/>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A22:A28"/>
-    <mergeCell ref="F22:F28"/>
     <mergeCell ref="F14:F21"/>
+    <mergeCell ref="A22:A31"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:F31"/>
+    <mergeCell ref="B24:E24"/>
   </mergeCells>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F22" r:id="rId1"/>
-    <hyperlink ref="F13" r:id="rId2"/>
+    <hyperlink ref="F13" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="F22" r:id="rId2" xr:uid="{5F505D9E-DB4E-4344-8A9C-D6505920531D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -7411,18 +8157,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="68.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="68.7265625" style="2" customWidth="1"/>
     <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="5" width="61.28515625" customWidth="1"/>
+    <col min="5" max="5" width="61.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -7439,68 +8185,68 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="165" t="s">
+    <row r="2" spans="1:5" ht="21.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="201" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="124" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="149" t="s">
-        <v>412</v>
-      </c>
-      <c r="D2" s="150" t="s">
+      <c r="C2" s="125" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="126" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="151"/>
-    </row>
-    <row r="3" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="166"/>
+      <c r="E2" s="127"/>
+    </row>
+    <row r="3" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="202"/>
       <c r="B3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="152" t="s">
-        <v>194</v>
+      <c r="C3" s="128" t="s">
+        <v>192</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="152" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="166"/>
+      <c r="E3" s="128" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="202"/>
       <c r="B4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="152" t="s">
-        <v>402</v>
+      <c r="C4" s="128" t="s">
+        <v>373</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E4" s="152" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="167"/>
+      <c r="E4" s="128" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="203"/>
       <c r="B5" s="11" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="C5" s="76" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" s="76" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="197" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="210" t="s">
         <v>133</v>
       </c>
       <c r="B6" s="22" t="s">
@@ -7511,19 +8257,19 @@
       </c>
       <c r="D6" s="24">
         <f>DIA!D4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="198"/>
+    <row r="7" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="211"/>
       <c r="B7" s="22" t="s">
         <v>130</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D7" s="37">
         <f>SpectraSimilarity!D8</f>
@@ -7533,8 +8279,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+    <row r="8" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="211"/>
       <c r="B8" s="22" t="s">
         <v>141</v>
       </c>
@@ -7549,23 +8295,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199"/>
-      <c r="B9" s="145" t="s">
-        <v>401</v>
-      </c>
-      <c r="C9" s="146" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="147" t="b">
+    <row r="9" spans="1:5" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="212"/>
+      <c r="B9" s="121" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="123" t="b">
         <f>SpectraSimilarity!D13</f>
         <v>1</v>
       </c>
-      <c r="E9" s="146" t="s">
+      <c r="E9" s="122" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A5"/>
@@ -7577,19 +8323,19 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" customWidth="1"/>
     <col min="3" max="3" width="74" style="2" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="77.7109375" customWidth="1"/>
-    <col min="6" max="6" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77.7265625" customWidth="1"/>
+    <col min="6" max="6" width="47.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -7602,15 +8348,15 @@
       <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="110" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="200" t="s">
+      <c r="F1" s="14" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="213" t="s">
         <v>139</v>
       </c>
       <c r="B2" s="34" t="s">
@@ -7621,17 +8367,17 @@
       </c>
       <c r="D2" s="36">
         <f>FSDB!D6</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="107" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="202" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="179"/>
+      <c r="F2" s="215" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="182"/>
       <c r="B3" s="4" t="s">
         <v>109</v>
       </c>
@@ -7639,33 +8385,33 @@
         <v>36</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="E3" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="201"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179"/>
+        <v>305</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>306</v>
+      </c>
+      <c r="F3" s="214"/>
+    </row>
+    <row r="4" spans="1:6" ht="49.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="182"/>
       <c r="B4" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E4" s="109" t="s">
-        <v>293</v>
-      </c>
-      <c r="F4" s="121" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="179"/>
+        <v>235</v>
+      </c>
+      <c r="E4" s="94" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="105" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="182"/>
       <c r="B5" s="18" t="s">
         <v>111</v>
       </c>
@@ -7673,195 +8419,195 @@
         <v>140</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="109" t="s">
-        <v>424</v>
-      </c>
-      <c r="F5" s="118"/>
-    </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="179"/>
+        <v>235</v>
+      </c>
+      <c r="E5" s="94" t="s">
+        <v>397</v>
+      </c>
+      <c r="F5" s="102"/>
+    </row>
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="182"/>
       <c r="B6" s="18" t="s">
         <v>112</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D6" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" s="94" t="s">
         <v>237</v>
       </c>
-      <c r="E6" s="109" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6" s="118"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="179"/>
+      <c r="F6" s="102"/>
+    </row>
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="182"/>
       <c r="B7" s="18" t="s">
         <v>113</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D7" s="18">
         <v>2</v>
       </c>
-      <c r="E7" s="109" t="s">
-        <v>299</v>
-      </c>
-      <c r="F7" s="118"/>
-    </row>
-    <row r="8" spans="1:6" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="179"/>
+      <c r="E7" s="94" t="s">
+        <v>292</v>
+      </c>
+      <c r="F7" s="102"/>
+    </row>
+    <row r="8" spans="1:6" ht="31.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="182"/>
       <c r="B8" s="18" t="s">
         <v>114</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8" s="18">
         <v>1</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="94" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="196" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="179"/>
+      <c r="F8" s="209" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="34.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="182"/>
       <c r="B9" s="18" t="s">
         <v>115</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" s="18">
         <v>20</v>
       </c>
-      <c r="E9" s="109" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="181"/>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="179"/>
+      <c r="E9" s="94" t="s">
+        <v>279</v>
+      </c>
+      <c r="F9" s="184"/>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="182"/>
       <c r="B10" s="18" t="s">
         <v>116</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D10" s="18">
         <v>50</v>
       </c>
-      <c r="E10" s="109" t="s">
+      <c r="E10" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="181"/>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="179"/>
+      <c r="F10" s="184"/>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="54.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="182"/>
       <c r="B11" s="18" t="s">
         <v>117</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D11" s="18">
         <v>1</v>
       </c>
-      <c r="E11" s="109" t="s">
-        <v>301</v>
-      </c>
-      <c r="F11" s="181"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="179"/>
+      <c r="E11" s="94" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="184"/>
+    </row>
+    <row r="12" spans="1:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="182"/>
       <c r="B12" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D12" s="18">
         <v>0.01</v>
       </c>
-      <c r="E12" s="108" t="s">
+      <c r="E12" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="181"/>
-    </row>
-    <row r="13" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="179"/>
+      <c r="F12" s="184"/>
+    </row>
+    <row r="13" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="182"/>
       <c r="B13" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D13" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="108" t="s">
+      <c r="E13" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="181"/>
-    </row>
-    <row r="14" spans="1:6" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="179"/>
+      <c r="F13" s="184"/>
+    </row>
+    <row r="14" spans="1:6" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="182"/>
       <c r="B14" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D14" s="18">
         <v>0</v>
       </c>
-      <c r="E14" s="108" t="s">
+      <c r="E14" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="181"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="179"/>
+      <c r="F14" s="184"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="182"/>
       <c r="B15" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D15" s="18">
         <v>2</v>
       </c>
-      <c r="E15" s="108" t="s">
+      <c r="E15" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="181"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="179"/>
+      <c r="F15" s="184"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="182"/>
       <c r="B16" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D16" s="18">
         <v>0.75</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="181"/>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="179"/>
+      <c r="F16" s="184"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="182"/>
       <c r="B17" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>132</v>
@@ -7869,47 +8615,47 @@
       <c r="D17" s="18">
         <v>0</v>
       </c>
-      <c r="E17" s="108" t="s">
+      <c r="E17" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="181"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="179"/>
+      <c r="F17" s="184"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="182"/>
       <c r="B18" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D18" s="18">
         <v>5</v>
       </c>
-      <c r="E18" s="108" t="s">
+      <c r="E18" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="201"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="179"/>
-      <c r="B19" s="117" t="s">
-        <v>238</v>
+      <c r="F18" s="214"/>
+    </row>
+    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="182"/>
+      <c r="B19" s="101" t="s">
+        <v>236</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D19" s="66">
         <v>0</v>
       </c>
-      <c r="E19" s="108" t="s">
-        <v>294</v>
-      </c>
-      <c r="F19" s="119"/>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="180"/>
-      <c r="B20" s="115" t="s">
-        <v>317</v>
+      <c r="E19" s="93" t="s">
+        <v>287</v>
+      </c>
+      <c r="F19" s="103"/>
+    </row>
+    <row r="20" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="183"/>
+      <c r="B20" s="99" t="s">
+        <v>310</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>50</v>
@@ -7917,12 +8663,12 @@
       <c r="D20" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="116" t="s">
+      <c r="E20" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="120"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="F20" s="104"/>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A20"/>
@@ -7930,9 +8676,9 @@
     <mergeCell ref="F2:F3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F8" r:id="rId1"/>
-    <hyperlink ref="F4" r:id="rId2" location="standardizing-precursor-types"/>
-    <hyperlink ref="F2" r:id="rId3"/>
+    <hyperlink ref="F8" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="F4" r:id="rId2" location="standardizing-precursor-types" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="F2" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -7940,18 +8686,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="67.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="67.54296875" style="2" customWidth="1"/>
     <col min="4" max="4" width="56" customWidth="1"/>
-    <col min="5" max="5" width="63.5703125" customWidth="1"/>
+    <col min="5" max="5" width="63.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="61.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -7968,15 +8714,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="68.45" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="203" t="s">
+    <row r="2" spans="1:5" ht="68.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="216" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="135" t="s">
-        <v>351</v>
+      <c r="C2" s="111" t="s">
+        <v>339</v>
       </c>
       <c r="D2" s="29" t="str">
         <f>DIA!D9</f>
@@ -7984,29 +8730,29 @@
       </c>
       <c r="E2" s="28"/>
     </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="204"/>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="217"/>
       <c r="B3" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="135" t="s">
+      <c r="C3" s="111" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="29">
         <f>SpectraSimilarity!D2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="28" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="204"/>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="217"/>
       <c r="B4" s="58" t="s">
         <v>123</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D4" s="60">
         <v>250</v>
@@ -8015,13 +8761,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="204"/>
+    <row r="5" spans="1:5" ht="25.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="217"/>
       <c r="B5" s="58" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D5" s="60">
         <v>20</v>
@@ -8030,8 +8776,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="204"/>
+    <row r="6" spans="1:5" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="217"/>
       <c r="B6" s="58" t="s">
         <v>125</v>
       </c>
@@ -8042,41 +8788,42 @@
         <v>1</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="204"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="217"/>
       <c r="B7" s="61" t="s">
         <v>126</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>271</v>
+        <v>428</v>
       </c>
       <c r="D7" s="63">
+        <f>CSA!D29</f>
         <v>0.05</v>
       </c>
       <c r="E7" s="62" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="204"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="217"/>
       <c r="B8" s="61" t="s">
         <v>127</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D8" s="63" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="E8" s="62" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="204"/>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="217"/>
       <c r="B9" s="61" t="s">
         <v>128</v>
       </c>
@@ -8087,11 +8834,11 @@
         <v>57</v>
       </c>
       <c r="E9" s="62" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="205"/>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="218"/>
       <c r="B10" s="31" t="s">
         <v>129</v>
       </c>
@@ -8102,10 +8849,10 @@
         <v>89</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A10"/>
@@ -8116,471 +8863,479 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A2:H51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="66.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="66.7265625" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="64" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H2" s="64"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>246</v>
-      </c>
-      <c r="C14" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="C26" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="67" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C38" s="67" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="C41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="65"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
